--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484698_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484698_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>1.7198</v>
+        <v>2.154</v>
       </c>
       <c r="E2" t="n">
-        <v>0.382</v>
+        <v>0.7665999999999999</v>
       </c>
       <c r="F2" t="n">
-        <v>1.3378</v>
+        <v>1.3874</v>
       </c>
       <c r="G2" t="n">
         <v>0.6973</v>
@@ -610,13 +610,13 @@
         <v>1.6493</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.6268</v>
+        <v>-0.1927</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.4774</v>
+        <v>-0.0927</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.1495</v>
+        <v>-0.0999</v>
       </c>
       <c r="V2" t="n">
         <v>0</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>M. LARA BARRACHINA</t>
+          <t>J. TORRES HERNANDO</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>1.4018</v>
+        <v>1.5942</v>
       </c>
       <c r="E3" t="n">
-        <v>3.3238</v>
+        <v>0.4116</v>
       </c>
       <c r="F3" t="n">
-        <v>-1.9221</v>
+        <v>1.1826</v>
       </c>
       <c r="G3" t="n">
-        <v>-2.6498</v>
+        <v>-0.398</v>
       </c>
       <c r="H3" t="n">
-        <v>-1.0436</v>
+        <v>-1.8063</v>
       </c>
       <c r="I3" t="n">
-        <v>-1.6062</v>
+        <v>1.4083</v>
       </c>
       <c r="J3" t="n">
-        <v>1.8932</v>
+        <v>1.2661</v>
       </c>
       <c r="K3" t="n">
-        <v>1.5757</v>
+        <v>-0.1425</v>
       </c>
       <c r="L3" t="n">
-        <v>0.3175</v>
+        <v>1.4086</v>
       </c>
       <c r="M3" t="n">
-        <v>-4.543</v>
+        <v>-1.6641</v>
       </c>
       <c r="N3" t="n">
-        <v>-2.6193</v>
+        <v>-1.6638</v>
       </c>
       <c r="O3" t="n">
-        <v>-1.9237</v>
+        <v>-0.0003</v>
       </c>
       <c r="P3" t="n">
-        <v>2.3823</v>
+        <v>1.8326</v>
       </c>
       <c r="Q3" t="n">
-        <v>-1.8326</v>
+        <v>-0.9163</v>
       </c>
       <c r="R3" t="n">
-        <v>4.2149</v>
+        <v>2.7489</v>
       </c>
       <c r="S3" t="n">
-        <v>1.0462</v>
+        <v>0.1597</v>
       </c>
       <c r="T3" t="n">
-        <v>0.7292999999999999</v>
+        <v>0.0619</v>
       </c>
       <c r="U3" t="n">
-        <v>0.3169</v>
+        <v>0.0978</v>
       </c>
       <c r="V3" t="n">
-        <v>0.6231</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>2.5339</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>-1.9109</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>H. VERNAZA DE LA FUENTE</t>
+          <t>M. LARA BARRACHINA</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.0452</v>
+        <v>1.4902</v>
       </c>
       <c r="E4" t="n">
-        <v>1.3845</v>
+        <v>3.4618</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.3392</v>
+        <v>-1.9716</v>
       </c>
       <c r="G4" t="n">
-        <v>0.2799</v>
+        <v>-2.6498</v>
       </c>
       <c r="H4" t="n">
-        <v>0.1517</v>
+        <v>-1.0436</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1282</v>
+        <v>-1.6062</v>
       </c>
       <c r="J4" t="n">
-        <v>1.0187</v>
+        <v>1.8932</v>
       </c>
       <c r="K4" t="n">
-        <v>1.0187</v>
+        <v>1.5757</v>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>0.3175</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.7388</v>
+        <v>-4.543</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.867</v>
+        <v>-2.6193</v>
       </c>
       <c r="O4" t="n">
-        <v>0.1282</v>
+        <v>-1.9237</v>
       </c>
       <c r="P4" t="n">
-        <v>0.3665</v>
+        <v>2.3823</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>-1.8326</v>
       </c>
       <c r="R4" t="n">
-        <v>0.3665</v>
+        <v>4.2149</v>
       </c>
       <c r="S4" t="n">
-        <v>0.3988</v>
+        <v>1.1346</v>
       </c>
       <c r="T4" t="n">
-        <v>0.3658</v>
+        <v>0.8673</v>
       </c>
       <c r="U4" t="n">
-        <v>0.033</v>
+        <v>0.2673</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>0.6231</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>2.5339</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>-1.9109</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>J. TORRES HERNANDO</t>
+          <t>H. VERNAZA DE LA FUENTE</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,58 +799,58 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.2886</v>
+        <v>0.9575</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.7701</v>
+        <v>1.2472</v>
       </c>
       <c r="F5" t="n">
-        <v>1.0587</v>
+        <v>-0.2897</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.398</v>
+        <v>0.2799</v>
       </c>
       <c r="H5" t="n">
-        <v>-1.8063</v>
+        <v>0.1517</v>
       </c>
       <c r="I5" t="n">
-        <v>1.4083</v>
+        <v>0.1282</v>
       </c>
       <c r="J5" t="n">
-        <v>1.2661</v>
+        <v>1.0187</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.1425</v>
+        <v>1.0187</v>
       </c>
       <c r="L5" t="n">
-        <v>1.4086</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.6641</v>
+        <v>-0.7388</v>
       </c>
       <c r="N5" t="n">
-        <v>-1.6638</v>
+        <v>-0.867</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.0003</v>
+        <v>0.1282</v>
       </c>
       <c r="P5" t="n">
-        <v>1.8326</v>
+        <v>0.3665</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.9163</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>2.7489</v>
+        <v>0.3665</v>
       </c>
       <c r="S5" t="n">
-        <v>-1.1459</v>
+        <v>0.3111</v>
       </c>
       <c r="T5" t="n">
-        <v>-1.1199</v>
+        <v>0.2285</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.026</v>
+        <v>0.08260000000000001</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.0166</v>
+        <v>-0.3378</v>
       </c>
       <c r="E6" t="n">
-        <v>1.2755</v>
+        <v>0.9459</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.2589</v>
+        <v>-1.2837</v>
       </c>
       <c r="G6" t="n">
         <v>-0.5861</v>
@@ -922,13 +922,13 @@
         <v>1.4661</v>
       </c>
       <c r="S6" t="n">
-        <v>1.3198</v>
+        <v>0.9655</v>
       </c>
       <c r="T6" t="n">
-        <v>0.7308</v>
+        <v>0.4012</v>
       </c>
       <c r="U6" t="n">
-        <v>0.5891</v>
+        <v>0.5643</v>
       </c>
       <c r="V6" t="n">
         <v>-1.267</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-3.4676</v>
+        <v>-3.1156</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.7059</v>
+        <v>-1.4035</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.7617</v>
+        <v>-1.7122</v>
       </c>
       <c r="G7" t="n">
         <v>-1.4456</v>
@@ -1000,13 +1000,13 @@
         <v>0.733</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.5718</v>
+        <v>-0.2198</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.2753</v>
+        <v>0.0272</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.2965</v>
+        <v>-0.247</v>
       </c>
       <c r="V7" t="n">
         <v>-1.267</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>D. SAEZ GIL</t>
+          <t>J. BALFAGON MIRAVET</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-5.3234</v>
+        <v>-5.1043</v>
       </c>
       <c r="E8" t="n">
-        <v>-3.5095</v>
+        <v>-4.8209</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.8139</v>
+        <v>-0.2834</v>
       </c>
       <c r="G8" t="n">
-        <v>-10.7144</v>
+        <v>-5.001</v>
       </c>
       <c r="H8" t="n">
-        <v>-5.3998</v>
+        <v>-2.0392</v>
       </c>
       <c r="I8" t="n">
-        <v>-5.3146</v>
+        <v>-2.9618</v>
       </c>
       <c r="J8" t="n">
-        <v>-5.9868</v>
+        <v>-1.4532</v>
       </c>
       <c r="K8" t="n">
-        <v>-2.3073</v>
+        <v>-0.4151</v>
       </c>
       <c r="L8" t="n">
-        <v>-3.6795</v>
+        <v>-1.0381</v>
       </c>
       <c r="M8" t="n">
-        <v>-4.7276</v>
+        <v>-3.5478</v>
       </c>
       <c r="N8" t="n">
-        <v>-3.0925</v>
+        <v>-1.6241</v>
       </c>
       <c r="O8" t="n">
-        <v>-1.6351</v>
+        <v>-1.9237</v>
       </c>
       <c r="P8" t="n">
-        <v>0.733</v>
+        <v>-0.733</v>
       </c>
       <c r="Q8" t="n">
-        <v>-2.7489</v>
+        <v>-4.5814</v>
       </c>
       <c r="R8" t="n">
-        <v>3.4819</v>
+        <v>3.8484</v>
       </c>
       <c r="S8" t="n">
-        <v>1.8021</v>
+        <v>0.6401</v>
       </c>
       <c r="T8" t="n">
-        <v>2.0483</v>
+        <v>0.5698</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.2462</v>
+        <v>0.0703</v>
       </c>
       <c r="V8" t="n">
-        <v>2.8559</v>
+        <v>-0.0104</v>
       </c>
       <c r="W8" t="n">
-        <v>3.1778</v>
+        <v>0.6439</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.3219</v>
+        <v>-0.6543</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>J. BALFAGON MIRAVET</t>
+          <t>D. SAEZ GIL</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-5.5501</v>
+        <v>-6.0781</v>
       </c>
       <c r="E9" t="n">
-        <v>-5.1923</v>
+        <v>-4.3881</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.3577</v>
+        <v>-1.6901</v>
       </c>
       <c r="G9" t="n">
-        <v>-5.001</v>
+        <v>-10.7144</v>
       </c>
       <c r="H9" t="n">
-        <v>-2.0392</v>
+        <v>-5.3998</v>
       </c>
       <c r="I9" t="n">
-        <v>-2.9618</v>
+        <v>-5.3146</v>
       </c>
       <c r="J9" t="n">
-        <v>-1.4532</v>
+        <v>-5.9868</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.4151</v>
+        <v>-2.3073</v>
       </c>
       <c r="L9" t="n">
-        <v>-1.0381</v>
+        <v>-3.6795</v>
       </c>
       <c r="M9" t="n">
-        <v>-3.5478</v>
+        <v>-4.7276</v>
       </c>
       <c r="N9" t="n">
-        <v>-1.6241</v>
+        <v>-3.0925</v>
       </c>
       <c r="O9" t="n">
-        <v>-1.9237</v>
+        <v>-1.6351</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.733</v>
+        <v>0.733</v>
       </c>
       <c r="Q9" t="n">
-        <v>-4.5814</v>
+        <v>-2.7489</v>
       </c>
       <c r="R9" t="n">
-        <v>3.8484</v>
+        <v>3.4819</v>
       </c>
       <c r="S9" t="n">
-        <v>0.1944</v>
+        <v>1.0473</v>
       </c>
       <c r="T9" t="n">
-        <v>0.1984</v>
+        <v>1.1697</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.004</v>
+        <v>-0.1224</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.0104</v>
+        <v>2.8559</v>
       </c>
       <c r="W9" t="n">
-        <v>0.6439</v>
+        <v>3.1778</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.6543</v>
+        <v>-0.3219</v>
       </c>
     </row>
     <row r="10">
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-7.1043</v>
+        <v>-6.8819</v>
       </c>
       <c r="E10" t="n">
-        <v>-4.9723</v>
+        <v>-4.3536</v>
       </c>
       <c r="F10" t="n">
-        <v>-2.132</v>
+        <v>-2.5284</v>
       </c>
       <c r="G10" t="n">
         <v>-6.8009</v>
@@ -1234,13 +1234,13 @@
         <v>2.5656</v>
       </c>
       <c r="S10" t="n">
-        <v>0.2305</v>
+        <v>0.4529</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.2956</v>
+        <v>0.3232</v>
       </c>
       <c r="U10" t="n">
-        <v>0.5261</v>
+        <v>0.1297</v>
       </c>
       <c r="V10" t="n">
         <v>-1.267</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-16.9734</v>
+        <v>-15.3218</v>
       </c>
       <c r="E11" t="n">
-        <v>-9.784300000000002</v>
+        <v>-8.132999999999999</v>
       </c>
       <c r="F11" t="n">
-        <v>-7.189</v>
+        <v>-7.1891</v>
       </c>
       <c r="G11" t="n">
         <v>-26.6186</v>
@@ -1288,7 +1288,7 @@
         <v>-4.300199999999999</v>
       </c>
       <c r="K11" t="n">
-        <v>-1.098000000000001</v>
+        <v>-1.098</v>
       </c>
       <c r="L11" t="n">
         <v>-3.2022</v>
@@ -1312,13 +1312,13 @@
         <v>21.0746</v>
       </c>
       <c r="S11" t="n">
-        <v>2.6473</v>
+        <v>4.298699999999999</v>
       </c>
       <c r="T11" t="n">
-        <v>1.904399999999999</v>
+        <v>3.5561</v>
       </c>
       <c r="U11" t="n">
-        <v>0.7429</v>
+        <v>0.7427</v>
       </c>
       <c r="V11" t="n">
         <v>-0.3323999999999998</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>8.9529</v>
+        <v>8.7271</v>
       </c>
       <c r="E12" t="n">
-        <v>5.2382</v>
+        <v>4.2767</v>
       </c>
       <c r="F12" t="n">
-        <v>3.7147</v>
+        <v>4.4504</v>
       </c>
       <c r="G12" t="n">
         <v>7.1128</v>
@@ -1390,13 +1390,13 @@
         <v>2.7489</v>
       </c>
       <c r="S12" t="n">
-        <v>0.534</v>
+        <v>0.3082</v>
       </c>
       <c r="T12" t="n">
-        <v>1.1335</v>
+        <v>0.172</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.5995</v>
+        <v>0.1363</v>
       </c>
       <c r="V12" t="n">
         <v>2.2224</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>5.4351</v>
+        <v>4.7983</v>
       </c>
       <c r="E13" t="n">
-        <v>3.1666</v>
+        <v>2.6858</v>
       </c>
       <c r="F13" t="n">
-        <v>2.2685</v>
+        <v>2.1124</v>
       </c>
       <c r="G13" t="n">
         <v>6.2439</v>
@@ -1468,13 +1468,13 @@
         <v>2.3823</v>
       </c>
       <c r="S13" t="n">
-        <v>1.097</v>
+        <v>0.4602</v>
       </c>
       <c r="T13" t="n">
-        <v>0.5475</v>
+        <v>0.0668</v>
       </c>
       <c r="U13" t="n">
-        <v>0.5495</v>
+        <v>0.3934</v>
       </c>
       <c r="V13" t="n">
         <v>-0.6231</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>J. CHALER ROMERO</t>
+          <t>M. AROCA RUBIO</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,64 +1501,64 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>1.7853</v>
+        <v>3.1999</v>
       </c>
       <c r="E14" t="n">
-        <v>0.0259</v>
+        <v>0.9875</v>
       </c>
       <c r="F14" t="n">
-        <v>1.7594</v>
+        <v>2.2124</v>
       </c>
       <c r="G14" t="n">
-        <v>4.6348</v>
+        <v>3.8323</v>
       </c>
       <c r="H14" t="n">
-        <v>0.8361</v>
+        <v>1.015</v>
       </c>
       <c r="I14" t="n">
-        <v>3.7987</v>
+        <v>2.8173</v>
       </c>
       <c r="J14" t="n">
-        <v>3.4905</v>
+        <v>2.9723</v>
       </c>
       <c r="K14" t="n">
-        <v>0.2043</v>
+        <v>0.7954</v>
       </c>
       <c r="L14" t="n">
-        <v>3.2862</v>
+        <v>2.1769</v>
       </c>
       <c r="M14" t="n">
-        <v>1.1443</v>
+        <v>0.86</v>
       </c>
       <c r="N14" t="n">
-        <v>0.6318</v>
+        <v>0.2196</v>
       </c>
       <c r="O14" t="n">
-        <v>0.5125</v>
+        <v>0.6404</v>
       </c>
       <c r="P14" t="n">
-        <v>-0.5498</v>
+        <v>-2.7489</v>
       </c>
       <c r="Q14" t="n">
-        <v>-2.7489</v>
+        <v>-5.4977</v>
       </c>
       <c r="R14" t="n">
-        <v>2.1991</v>
+        <v>2.7489</v>
       </c>
       <c r="S14" t="n">
-        <v>-1.0327</v>
+        <v>-0.4384</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.7157</v>
+        <v>-0.3088</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.3171</v>
+        <v>-0.1296</v>
       </c>
       <c r="V14" t="n">
-        <v>-1.267</v>
+        <v>2.5548</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>3.8217</v>
       </c>
       <c r="X14" t="n">
         <v>-1.267</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>M. AROCA RUBIO</t>
+          <t>J. CHALER ROMERO</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,64 +1579,64 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.7356</v>
+        <v>2.4293</v>
       </c>
       <c r="E15" t="n">
-        <v>0.5068</v>
+        <v>0.3144</v>
       </c>
       <c r="F15" t="n">
-        <v>1.2288</v>
+        <v>2.1149</v>
       </c>
       <c r="G15" t="n">
-        <v>3.8323</v>
+        <v>4.6348</v>
       </c>
       <c r="H15" t="n">
-        <v>1.015</v>
+        <v>0.8361</v>
       </c>
       <c r="I15" t="n">
-        <v>2.8173</v>
+        <v>3.7987</v>
       </c>
       <c r="J15" t="n">
-        <v>2.9723</v>
+        <v>3.4905</v>
       </c>
       <c r="K15" t="n">
-        <v>0.7954</v>
+        <v>0.2043</v>
       </c>
       <c r="L15" t="n">
-        <v>2.1769</v>
+        <v>3.2862</v>
       </c>
       <c r="M15" t="n">
-        <v>0.86</v>
+        <v>1.1443</v>
       </c>
       <c r="N15" t="n">
-        <v>0.2196</v>
+        <v>0.6318</v>
       </c>
       <c r="O15" t="n">
-        <v>0.6404</v>
+        <v>0.5125</v>
       </c>
       <c r="P15" t="n">
+        <v>-0.5498</v>
+      </c>
+      <c r="Q15" t="n">
         <v>-2.7489</v>
       </c>
-      <c r="Q15" t="n">
-        <v>-5.4977</v>
-      </c>
       <c r="R15" t="n">
-        <v>2.7489</v>
+        <v>2.1991</v>
       </c>
       <c r="S15" t="n">
-        <v>-1.9026</v>
+        <v>-0.3888</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.7896</v>
+        <v>-0.4272</v>
       </c>
       <c r="U15" t="n">
-        <v>-1.1131</v>
+        <v>0.0384</v>
       </c>
       <c r="V15" t="n">
-        <v>2.5548</v>
+        <v>-1.267</v>
       </c>
       <c r="W15" t="n">
-        <v>3.8217</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
         <v>-1.267</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A. VILLALBA MOLLA</t>
+          <t>C. GARCIA SAHUQUILLO</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.4192</v>
+        <v>1.5087</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.434</v>
+        <v>2.5839</v>
       </c>
       <c r="F16" t="n">
-        <v>1.8532</v>
+        <v>-1.0752</v>
       </c>
       <c r="G16" t="n">
-        <v>0.4824</v>
+        <v>4.3511</v>
       </c>
       <c r="H16" t="n">
-        <v>0.3736</v>
+        <v>2.1038</v>
       </c>
       <c r="I16" t="n">
-        <v>0.1088</v>
+        <v>2.2472</v>
       </c>
       <c r="J16" t="n">
-        <v>0.6293</v>
+        <v>3.6891</v>
       </c>
       <c r="K16" t="n">
-        <v>0.5202</v>
+        <v>2.2108</v>
       </c>
       <c r="L16" t="n">
-        <v>0.1091</v>
+        <v>1.4783</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.1469</v>
+        <v>0.662</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.1466</v>
+        <v>-0.1069</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.0003</v>
+        <v>0.7689</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>1.0995</v>
       </c>
       <c r="Q16" t="n">
         <v>-0.9163</v>
       </c>
       <c r="R16" t="n">
-        <v>0.9163</v>
+        <v>2.0158</v>
       </c>
       <c r="S16" t="n">
-        <v>0.3137</v>
+        <v>-0.141</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.1471</v>
+        <v>-0.1889</v>
       </c>
       <c r="U16" t="n">
-        <v>0.4608</v>
+        <v>0.0479</v>
       </c>
       <c r="V16" t="n">
-        <v>0.6231</v>
+        <v>-3.8009</v>
       </c>
       <c r="W16" t="n">
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>0.6231</v>
+        <v>-3.8009</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>J. VILLARROYA FELIPO</t>
+          <t>A. VILLALBA MOLLA</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.0864</v>
+        <v>1.2442</v>
       </c>
       <c r="E17" t="n">
-        <v>0.4683</v>
+        <v>-0.2417</v>
       </c>
       <c r="F17" t="n">
-        <v>0.6181</v>
+        <v>1.4859</v>
       </c>
       <c r="G17" t="n">
-        <v>0.9142</v>
+        <v>0.4824</v>
       </c>
       <c r="H17" t="n">
-        <v>1.0007</v>
+        <v>0.3736</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.08649999999999999</v>
+        <v>0.1088</v>
       </c>
       <c r="J17" t="n">
-        <v>0.4502</v>
+        <v>0.6293</v>
       </c>
       <c r="K17" t="n">
-        <v>1.0496</v>
+        <v>0.5202</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.5994</v>
+        <v>0.1091</v>
       </c>
       <c r="M17" t="n">
-        <v>0.464</v>
+        <v>-0.1469</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.0489</v>
+        <v>-0.1466</v>
       </c>
       <c r="O17" t="n">
-        <v>0.5128</v>
+        <v>-0.0003</v>
       </c>
       <c r="P17" t="n">
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>-0.9163</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>0.9163</v>
       </c>
       <c r="S17" t="n">
-        <v>0.1722</v>
+        <v>0.1387</v>
       </c>
       <c r="T17" t="n">
-        <v>0.0181</v>
+        <v>0.0453</v>
       </c>
       <c r="U17" t="n">
-        <v>0.1541</v>
+        <v>0.0935</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>0.6231</v>
       </c>
       <c r="W17" t="n">
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>0.6231</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>C. GARCIA SAHUQUILLO</t>
+          <t>J. VILLARROYA FELIPO</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.8151</v>
+        <v>1.2351</v>
       </c>
       <c r="E18" t="n">
-        <v>2.2954</v>
+        <v>0.4683</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.4803</v>
+        <v>0.7667</v>
       </c>
       <c r="G18" t="n">
-        <v>4.3511</v>
+        <v>0.9142</v>
       </c>
       <c r="H18" t="n">
-        <v>2.1038</v>
+        <v>1.0007</v>
       </c>
       <c r="I18" t="n">
-        <v>2.2472</v>
+        <v>-0.08649999999999999</v>
       </c>
       <c r="J18" t="n">
-        <v>3.6891</v>
+        <v>0.4502</v>
       </c>
       <c r="K18" t="n">
-        <v>2.2108</v>
+        <v>1.0496</v>
       </c>
       <c r="L18" t="n">
-        <v>1.4783</v>
+        <v>-0.5994</v>
       </c>
       <c r="M18" t="n">
-        <v>0.662</v>
+        <v>0.464</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.1069</v>
+        <v>-0.0489</v>
       </c>
       <c r="O18" t="n">
-        <v>0.7689</v>
+        <v>0.5128</v>
       </c>
       <c r="P18" t="n">
-        <v>1.0995</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>-0.9163</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>2.0158</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.8345</v>
+        <v>0.3209</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.4774</v>
+        <v>0.0181</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.3572</v>
+        <v>0.3028</v>
       </c>
       <c r="V18" t="n">
-        <v>-3.8009</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-3.8009</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-4.2563</v>
+        <v>-3.605</v>
       </c>
       <c r="E19" t="n">
-        <v>-4.0782</v>
+        <v>-3.8859</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.1781</v>
+        <v>0.2809</v>
       </c>
       <c r="G19" t="n">
         <v>-0.953</v>
@@ -1936,13 +1936,13 @@
         <v>0.733</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.9942</v>
+        <v>-0.343</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.3122</v>
+        <v>-0.1199</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.6820000000000001</v>
+        <v>-0.2231</v>
       </c>
       <c r="V19" t="n">
         <v>0.6231</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>16.9733</v>
+        <v>19.5376</v>
       </c>
       <c r="E20" t="n">
         <v>7.189</v>
       </c>
       <c r="F20" t="n">
-        <v>9.784299999999998</v>
+        <v>12.3484</v>
       </c>
       <c r="G20" t="n">
         <v>26.6185</v>
@@ -2014,13 +2014,13 @@
         <v>13.7443</v>
       </c>
       <c r="S20" t="n">
-        <v>-2.6471</v>
+        <v>-0.08319999999999997</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.7429</v>
+        <v>-0.7425999999999999</v>
       </c>
       <c r="U20" t="n">
-        <v>-1.9045</v>
+        <v>0.6596000000000001</v>
       </c>
       <c r="V20" t="n">
         <v>0.3324000000000003</v>
